--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-01.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-01.xlsx
@@ -954,7 +954,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583981122350</v>
+        <v>5583998112250</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
